--- a/reports/pdf_change_20261013.xlsx
+++ b/reports/pdf_change_20261013.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,11 +38,37 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -49,11 +77,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,11 +114,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -75,6 +142,40 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -466,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 0/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, RISE, TIGER</t>
+          <t>캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 7억(0.1%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -487,78 +588,330 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>1675211556</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.96%→1.37%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>70→92</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오  (편출)</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-656364626</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.12%→0.00%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>46→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1454221614</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>3.40%→3.45%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>211→230</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-719662809</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.53%→0.39%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>71→52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>517880863</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.01%→1.16%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>135→148</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-896699762</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>2.63%→2.43%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>222→207</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>479219873</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>1.11%→1.22%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>120→130</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-858479772</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.86%→0.64%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>48→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>1472449609</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>1.14%→1.44%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>20→25</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-784979792</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.24%→0.09%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>14→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-475691874</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>5.50%→5.60%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>183→180</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 26억(0.8%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -572,34 +925,358 @@
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억   ·   현금 33억(1.2%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억   ·   현금 11억(0.5%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 1종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>5758366788</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>11.90%→15.45%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>367→451</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-231</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-3291749307</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>6.46%→4.42%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>852→621</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-1935339593</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>11.75%→10.90%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>270→248</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-84302982</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>3.14%→3.17%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>686→677</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>인벤티지랩</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-46644990</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→2.56%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>555→550</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-69311985</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>3.31%→3.27%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>382→378</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 4억(1.1%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
+      <c r="K33" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="16">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A28:K28"/>
     <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20261013.xlsx
+++ b/reports/pdf_change_20261013.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 7억(0.1%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 5종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,163억      당일 2026-10-13  vs  전영업일 2026-10-12      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1675211556</v>
+        <v>1694016015</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-46</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-656364626</v>
+        <v>-663732401</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1454221614</v>
+        <v>1470545434</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-19</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-719662809</v>
+        <v>-727741114</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>517880863</v>
+        <v>523694140</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-15</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-896699762</v>
+        <v>-906765329</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>479219873</v>
+        <v>484599176</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-10</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-858479772</v>
+        <v>-868116315</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1472449609</v>
+        <v>1488978041</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-9</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-784979792</v>
+        <v>-793791288</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-3</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-475691874</v>
+        <v>-481031575</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 26억(0.8%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,174억      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -935,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억   ·   현금 33억(1.2%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,664억      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -959,7 +959,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억   ·   현금 11억(0.5%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 1종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억      당일 2026-10-13  vs  전영업일 2026-10-12      매수 1종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1055,7 +1055,7 @@
         <v>84</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>5758366788</v>
+        <v>5803826072</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>-231</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-3291749307</v>
+        <v>-3317735941</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>-22</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1935339593</v>
+        <v>-1950618083</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>-9</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-84302982</v>
+        <v>-84968510</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-46644990</v>
+        <v>-47013228</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>-4</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-69311985</v>
+        <v>-69859167</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 4억(1.1%)      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억      당일 2026-10-13  vs  전영업일 2026-10-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
